--- a/data/trans_orig/P21D6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163709</t>
+          <t>165028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196066</t>
+          <t>194969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115483</t>
+          <t>114023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134220</t>
+          <t>133923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287241</t>
+          <t>287157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325973</t>
+          <t>325309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>46173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>166421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191390</t>
+          <t>191137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254776</t>
+          <t>253475</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281991</t>
+          <t>281257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>428143</t>
+          <t>429560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>468732</t>
+          <t>469134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>58547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181127</t>
+          <t>180625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200061</t>
+          <t>200408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212761</t>
+          <t>213056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230783</t>
+          <t>229822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401127</t>
+          <t>400556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427460</t>
+          <t>426782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38412</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>65417</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>444991</t>
+          <t>445965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>275848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292613</t>
+          <t>293570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>229224</t>
+          <t>246367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>739331</t>
+          <t>734437</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>450903</t>
+          <t>445580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>81157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599957</t>
+          <t>588143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192648</t>
+          <t>193424</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213424</t>
+          <t>213493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176287</t>
+          <t>176343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193467</t>
+          <t>194182</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>375830</t>
+          <t>374990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>402781</t>
+          <t>401996</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40351</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>134665</t>
+          <t>133407</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146032</t>
+          <t>146203</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144104</t>
+          <t>143890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158508</t>
+          <t>158783</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>281796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>301432</t>
+          <t>301123</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>17012</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105279</t>
+          <t>106302</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>114580</t>
+          <t>114918</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>140890</t>
+          <t>139919</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>152778</t>
+          <t>153062</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>250213</t>
+          <t>249942</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>265733</t>
+          <t>265964</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>788091</t>
+          <t>748311</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1471616</t>
+          <t>1473332</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1357003</t>
+          <t>1362623</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1416388</t>
+          <t>1420515</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1952680</t>
+          <t>2021445</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2857998</t>
+          <t>2867653</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>146098</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>851847</t>
+          <t>899489</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,82 +4841,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>148365</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>168345</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>524495</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>289109</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>1167496</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>148365</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>125826</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>172880</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>524495</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>294341</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>1229180</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>88497</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>184190</t>
+          <t>189366</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>165028</t>
+          <t>170162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194969</t>
+          <t>201912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>126871</t>
+          <t>146696</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114023</t>
+          <t>133204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133923</t>
+          <t>155206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>311060</t>
+          <t>336062</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287157</t>
+          <t>313368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325309</t>
+          <t>351866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33450</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46173</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>180871</t>
+          <t>202801</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166421</t>
+          <t>188548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191137</t>
+          <t>213832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>267999</t>
+          <t>226361</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253475</t>
+          <t>214661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281257</t>
+          <t>234892</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>448870</t>
+          <t>429161</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>429560</t>
+          <t>412148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>469134</t>
+          <t>443402</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>57154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>192274</t>
+          <t>229464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180625</t>
+          <t>217403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200408</t>
+          <t>238532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>222361</t>
+          <t>258572</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213056</t>
+          <t>247773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>229822</t>
+          <t>266943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>414635</t>
+          <t>488036</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400556</t>
+          <t>472994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>426782</t>
+          <t>500999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65417</t>
+          <t>66904</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>234300</t>
+          <t>264994</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>248135</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>445965</t>
+          <t>277566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>285039</t>
+          <t>306924</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275848</t>
+          <t>296905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>519339</t>
+          <t>571917</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246367</t>
+          <t>553424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>734437</t>
+          <t>587027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>280504</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>445580</t>
+          <t>54755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>35745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>304882</t>
+          <t>66091</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>588143</t>
+          <t>82177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204379</t>
+          <t>222732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193424</t>
+          <t>210914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213493</t>
+          <t>232589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>185345</t>
+          <t>209033</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176343</t>
+          <t>199320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>194182</t>
+          <t>218264</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>389724</t>
+          <t>431766</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>374990</t>
+          <t>416839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>401996</t>
+          <t>446632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>42694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51104</t>
+          <t>54765</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>66778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>140772</t>
+          <t>155576</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>133407</t>
+          <t>147963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>161653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>151569</t>
+          <t>162410</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>143890</t>
+          <t>153825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158783</t>
+          <t>170232</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>292341</t>
+          <t>317987</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>281796</t>
+          <t>306338</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>301123</t>
+          <t>327899</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>36461</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>45826</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>501</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>111237</t>
+          <t>122387</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106302</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>114918</t>
+          <t>126012</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>147331</t>
+          <t>161949</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>139919</t>
+          <t>155166</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153062</t>
+          <t>168752</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>258569</t>
+          <t>284336</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>249942</t>
+          <t>275766</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>265964</t>
+          <t>292262</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1248024</t>
+          <t>1387320</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>748311</t>
+          <t>1354637</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1473332</t>
+          <t>1414435</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1386513</t>
+          <t>1471945</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1362623</t>
+          <t>1446899</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1420515</t>
+          <t>1496572</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2634537</t>
+          <t>2859264</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2021445</t>
+          <t>2821703</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2867653</t>
+          <t>2897449</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>376130</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>146098</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>899489</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>148365</t>
+          <t>161669</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>122343</t>
+          <t>143916</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>168345</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>524495</t>
+          <t>300998</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>289109</t>
+          <t>267562</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1167496</t>
+          <t>335956</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48386</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>67086</t>
+          <t>71543</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>88497</t>
+          <t>89490</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
